--- a/ميكانيكا ترم اول.xlsx
+++ b/ميكانيكا ترم اول.xlsx
@@ -2533,16 +2533,16 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J4">
         <v>8</v>
       </c>
       <c r="K4">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -4249,16 +4249,16 @@
         <v>14</v>
       </c>
       <c r="G26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J26">
         <v>14</v>
       </c>
       <c r="K26">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -4345,16 +4345,16 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H29">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J29">
         <v>6</v>
       </c>
       <c r="K29">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -7428,10 +7428,10 @@
         <v>18</v>
       </c>
       <c r="J30">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K30">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
@@ -7643,10 +7643,10 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="K5">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
